--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16803028</v>
+        <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>96990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bottenriket, Nrk</t>
+          <t>Kyrkmossen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520397</v>
+        <v>520415</v>
       </c>
       <c r="R2" t="n">
-        <v>6536998</v>
+        <v>6537054</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,17 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-23</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Medobservatör: Mats Andersson</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,80 +767,72 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16803028</t>
+          <t>https://artportalen.se/Sighting/137338712</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16619504</v>
+        <v>16803028</v>
       </c>
       <c r="B3" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bottenriken gammelskog, Nrk</t>
+          <t>Bottenriket, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520227</v>
+        <v>520397</v>
       </c>
       <c r="R3" t="n">
-        <v>6536945</v>
+        <v>6536998</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,17 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2009-07-07</t>
+          <t>2014-09-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-07-07</t>
+          <t>2014-09-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>observerad och artbestämd av Teppo Rämä, Olli Manninen, Sebastian Kirppu, Viktor Säfve, Sini Saarela m.fl.</t>
+          <t>Medobservatör: Mats Andersson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,85 +878,77 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>gammal barrblandskog</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16619504</t>
+          <t>https://artportalen.se/Sighting/16803028</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106674221</v>
+        <v>16619504</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kyrkmossemon, Bottenrikens gammelskogar, Nrk</t>
+          <t>Bottenriken gammelskog, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520420</v>
+        <v>520227</v>
       </c>
       <c r="R4" t="n">
-        <v>6537027</v>
+        <v>6536945</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
+          <t>2009-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
+          <t>2010-07-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>observerad och artbestämd av Teppo Rämä, Olli Manninen, Sebastian Kirppu, Viktor Säfve, Sini Saarela m.fl.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,56 +991,65 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106674221</t>
+          <t>https://artportalen.se/Sighting/16619504</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106642953</v>
+        <v>106674221</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1098,19 +1099,9 @@
           <t>2023-02-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,16 +1128,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106642953</t>
+          <t>https://artportalen.se/Sighting/106674221</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>97627229</v>
+        <v>106642953</v>
       </c>
       <c r="B6" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,25 +1145,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1181,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520397</v>
+        <v>520420</v>
       </c>
       <c r="R6" t="n">
-        <v>6536998</v>
+        <v>6537027</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,12 +1206,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2023-02-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2023-02-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,66 +1242,60 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97627229</t>
+          <t>https://artportalen.se/Sighting/106642953</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>97627078</v>
+        <v>97627229</v>
       </c>
       <c r="B7" t="n">
-        <v>5179</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkmossen, Bottenrikens gammelskogar, Nrk</t>
+          <t>Kyrkmossemon, Bottenrikens gammelskogar, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520465</v>
+        <v>520397</v>
       </c>
       <c r="R7" t="n">
-        <v>6536971</v>
+        <v>6536998</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,16 +1354,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97627078</t>
+          <t>https://artportalen.se/Sighting/97627229</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>106642888</v>
+        <v>97627078</v>
       </c>
       <c r="B8" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,42 +1371,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kyrkmossemon, Bottenrikens gammelskogar, Nrk</t>
+          <t>Kyrkmossen, Bottenrikens gammelskogar, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520421</v>
+        <v>520465</v>
       </c>
       <c r="R8" t="n">
-        <v>6536898</v>
+        <v>6536971</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,22 +1434,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1460,22 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum, Amanda Linderum</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106642888</t>
+          <t>https://artportalen.se/Sighting/97627078</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97627009</v>
+        <v>106642888</v>
       </c>
       <c r="B9" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1493,16 +1483,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1513,7 +1503,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1525,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520413</v>
+        <v>520421</v>
       </c>
       <c r="R9" t="n">
-        <v>6536996</v>
+        <v>6536898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,12 +1545,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2023-02-12</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2023-02-12</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Karlsson Linderum, Amanda Linderum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97627009</t>
+          <t>https://artportalen.se/Sighting/106642888</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106013756</v>
+        <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>97986</v>
+        <v>98267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1632,17 +1632,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kyrkmossemon, Bottenrikens gammelskogar, Nrk</t>
+          <t>Bottenriken, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520417</v>
+        <v>520177</v>
       </c>
       <c r="R10" t="n">
-        <v>6536946</v>
+        <v>6536897</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,13 +1698,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106013756</t>
+          <t>https://artportalen.se/Sighting/137338722</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106013759</v>
+        <v>97627009</v>
       </c>
       <c r="B11" t="n">
         <v>97986</v>
@@ -1735,7 +1735,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520421</v>
+        <v>520413</v>
       </c>
       <c r="R11" t="n">
-        <v>6536898</v>
+        <v>6536996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2021-12-19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,13 +1809,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106013759</t>
+          <t>https://artportalen.se/Sighting/97627009</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110929774</v>
+        <v>106013756</v>
       </c>
       <c r="B12" t="n">
         <v>97986</v>
@@ -1854,17 +1854,17 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bottenrikens gammelskogar, Nrk</t>
+          <t>Kyrkmossemon, Bottenrikens gammelskogar, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520275</v>
+        <v>520417</v>
       </c>
       <c r="R12" t="n">
-        <v>6536885</v>
+        <v>6536946</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,22 +1888,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-07-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,7 +1920,350 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/106013756</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>106013759</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kyrkmossemon, Bottenrikens gammelskogar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>520421</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6536898</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-01-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106013759</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110929774</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bottenrikens gammelskogar, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>520275</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6536885</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/110929774</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137338719</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98270</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bottenriken, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>520255</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6536869</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137338719</t>
         </is>
       </c>
     </row>
@@ -1947,6 +2280,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98270</v>
+        <v>98275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98275</v>
+        <v>98277</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98277</v>
+        <v>98283</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98283</v>
+        <v>98295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98295</v>
+        <v>98296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98296</v>
+        <v>98299</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 42867-2026 artfynd.xlsx
+++ b/artfynd/A 42867-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137338712</v>
       </c>
       <c r="B2" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1596,7 +1596,7 @@
         <v>137338722</v>
       </c>
       <c r="B10" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>137338719</v>
       </c>
       <c r="B15" t="n">
-        <v>98299</v>
+        <v>98303</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
